--- a/src/leetcode/Notes.xlsx
+++ b/src/leetcode/Notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I353174/X01/problem-solving/src/practice/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I353174/X01/problem-solving/src/leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DA9B25-9082-2741-A3D7-1172FFB5C517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D6CCFF-686E-3546-A099-8E5FA7264934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20260" xr2:uid="{78DCED3F-067B-3E4F-991A-F0C0F9E9847D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>Problem</t>
   </si>
@@ -296,6 +296,30 @@
   </si>
   <si>
     <t>String, Intersection, Characters</t>
+  </si>
+  <si>
+    <t>Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>Using map to keep track of unique characters, two pointers to expand and contract the sliding window</t>
+  </si>
+  <si>
+    <t>Sliding window</t>
+  </si>
+  <si>
+    <t>ZigZag Conversion</t>
+  </si>
+  <si>
+    <t>Create a n(total rows) String Builders and append one char at once for each String Builder</t>
+  </si>
+  <si>
+    <t>String Builder, Zig Zag, String</t>
+  </si>
+  <si>
+    <t>Reverse Integer</t>
+  </si>
+  <si>
+    <t>Reversing integer using division(/) and modulo (%) operator</t>
   </si>
 </sst>
 </file>
@@ -775,8 +799,8 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="96.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="95.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="68.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="41.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="33.83203125" style="1" customWidth="1"/>
@@ -924,14 +948,38 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
+    <row r="13" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="9"/>
+      <c r="A14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
@@ -973,6 +1021,9 @@
     <hyperlink ref="A10" r:id="rId9" xr:uid="{42C16418-E2C9-2643-AC18-029AFAEFB6B2}"/>
     <hyperlink ref="A11" r:id="rId10" xr:uid="{D99BB891-DCFB-1D43-8EE2-089A4A0B9129}"/>
     <hyperlink ref="A12" r:id="rId11" xr:uid="{8DE9C711-5DAE-4742-A757-D40C906FEC27}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{02DC47F7-CC70-7C4F-8AF1-779EFEF8B2F7}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{A736203A-E52D-EC4F-AC9E-CF8624FFC296}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{73840723-0B1E-BF4B-877A-91A3CEA566FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/leetcode/Notes.xlsx
+++ b/src/leetcode/Notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I353174/X01/problem-solving/src/leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D6CCFF-686E-3546-A099-8E5FA7264934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95325DAE-5B71-344E-B3A9-E11FA5109C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20260" xr2:uid="{78DCED3F-067B-3E4F-991A-F0C0F9E9847D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>Problem</t>
   </si>
@@ -320,6 +320,15 @@
   </si>
   <si>
     <t>Reversing integer using division(/) and modulo (%) operator</t>
+  </si>
+  <si>
+    <t>DNA Sequences</t>
+  </si>
+  <si>
+    <t>Sliding Window, Rolling Hash, Bit Manipulations</t>
+  </si>
+  <si>
+    <t>This can be done using sliding window or creating a sequences with bit manipulations or rolling hash (rabin karp)</t>
   </si>
 </sst>
 </file>
@@ -426,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -461,6 +470,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -800,7 +810,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="95.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="121.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="68.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="41.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="33.83203125" style="1" customWidth="1"/>
@@ -982,7 +992,15 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
+      <c r="A16" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="17" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="8"/>
@@ -1024,6 +1042,7 @@
     <hyperlink ref="A13" r:id="rId12" xr:uid="{02DC47F7-CC70-7C4F-8AF1-779EFEF8B2F7}"/>
     <hyperlink ref="A14" r:id="rId13" xr:uid="{A736203A-E52D-EC4F-AC9E-CF8624FFC296}"/>
     <hyperlink ref="A15" r:id="rId14" xr:uid="{73840723-0B1E-BF4B-877A-91A3CEA566FE}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{51B6D802-82B2-684F-84E8-59450A3B942C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/leetcode/Notes.xlsx
+++ b/src/leetcode/Notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I353174/X01/problem-solving/src/leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95325DAE-5B71-344E-B3A9-E11FA5109C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471F597E-4F23-E84B-9391-829462A97389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20260" xr2:uid="{78DCED3F-067B-3E4F-991A-F0C0F9E9847D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>Problem</t>
   </si>
@@ -329,6 +329,15 @@
   </si>
   <si>
     <t>This can be done using sliding window or creating a sequences with bit manipulations or rolling hash (rabin karp)</t>
+  </si>
+  <si>
+    <t>Bulls and cows</t>
+  </si>
+  <si>
+    <t>Postion intersection of Chars, and Union of Chars</t>
+  </si>
+  <si>
+    <t>With Single loop counting array</t>
   </si>
 </sst>
 </file>
@@ -1002,28 +1011,36 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="8"/>
-    </row>
-    <row r="18" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="8"/>
     </row>
-    <row r="19" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="8"/>
     </row>
-    <row r="20" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="8"/>
     </row>
-    <row r="21" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="8"/>
     </row>
-    <row r="22" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="8"/>
     </row>
-    <row r="23" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
     </row>
-    <row r="24" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
     </row>
   </sheetData>
@@ -1043,6 +1060,7 @@
     <hyperlink ref="A14" r:id="rId13" xr:uid="{A736203A-E52D-EC4F-AC9E-CF8624FFC296}"/>
     <hyperlink ref="A15" r:id="rId14" xr:uid="{73840723-0B1E-BF4B-877A-91A3CEA566FE}"/>
     <hyperlink ref="A16" r:id="rId15" xr:uid="{51B6D802-82B2-684F-84E8-59450A3B942C}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{D37F137D-9C8D-8D40-9409-F9B09C0D3E9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
